--- a/21_Fixed_Income_Rates/instances/benchmark_adversarial_bear_steepener.xlsx
+++ b/21_Fixed_Income_Rates/instances/benchmark_adversarial_bear_steepener.xlsx
@@ -9,18 +9,26 @@
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Assumptions" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Zero Curve" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Bond Analytics" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Portfolio" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Key Rate Risk" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Carry &amp; Roll" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Scenarios" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="P&amp;L Explain" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="Checks" sheetId="10" state="visible" r:id="rId12"/>
-    <sheet name="Sources" sheetId="11" state="visible" r:id="rId13"/>
-    <sheet name="RefreshLog" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="Institutional Surface" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Challenge Log" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Lineage Map" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Assumptions" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Zero Curve" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Bond Analytics" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Portfolio" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Key Rate Risk" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Carry &amp; Roll" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="Scenarios" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="P&amp;L Explain" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="Checks" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="Sources" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="RefreshLog" sheetId="15" state="visible" r:id="rId17"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="false" name="FS_DOMAIN" vbProcedure="false">'Institutional Surface'!$C$5</definedName>
+    <definedName function="false" hidden="false" name="FS_MATURITY" vbProcedure="false">'Institutional Surface'!$C$6</definedName>
+    <definedName function="false" hidden="false" name="FS_MODEL_ID" vbProcedure="false">'Institutional Surface'!$C$4</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -31,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="279">
   <si>
     <t xml:space="preserve">[PORTFOLIO / SECURITY] — Fixed Income &amp; Rates Model</t>
   </si>
@@ -105,6 +113,309 @@
     <t xml:space="preserve">PASS / REVIEW / FAIL must remain visible</t>
   </si>
   <si>
+    <t xml:space="preserve">Fixed Income &amp; Rates — Institutional Decision Surface</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed Income &amp; Rates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Declared maturity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canonical builder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tools/builders/build_fixed_income_release.py</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decision arena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trading desk, portfolio management, treasury, ALCO and independent risk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Committee artifact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">curve, carry and risk pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operating cadence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intraday desk; daily risk; monthly ALCO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Key decision outputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requirement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence / location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">price, yield, duration and convexity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">key-rate and spread DV01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">carry and roll-down</t>
+  </si>
+  <si>
+    <t xml:space="preserve">base, downside and break-even outputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">liquidity / funding requirement and binding constraint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insider questions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What part of carry is rolldown versus credit?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which curve and interpolation method is authoritative?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where does optionality invalidate duration?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which assumption is owner-approved versus modeler judgement?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What fails first and who must act?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scenario families</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parallel and nonparallel curve shocks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spread widening</t>
+  </si>
+  <si>
+    <t xml:space="preserve">basis and swap-spread move</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data freshness / source failure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">combined severe-but-plausible downside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary diligence documents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">security terms and prospectus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">curve construction policy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">repo / financing agreements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">approved model card and assumption register</t>
+  </si>
+  <si>
+    <t xml:space="preserve">independent validation and challenge record</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Challenge tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">price-yield monotonicity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">duration and convexity signs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">key-rate DV01 reconciles to parallel risk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">source-to-model lineage is reproducible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">units, signs, dates and legal definitions reconcile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Known failure modes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">using yield duration for callable instruments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mixing clean and dirty price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">failing to map off-the-run liquidity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stale vintage presented as current</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decision output disconnected from a binding constraint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulatory / methodological anchors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applicability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal Reserve SR 26-2 Model Risk Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">governance, validation, change control, monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.federalreserve.gov/supervisionreg/srletters/SR2602.htm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Map explicitly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basel SRP31 IRRBB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVE/NII, basis and option risk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.bis.org/basel_framework/chapter/SRP/31.htm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basel MAR21 Sensitivities-Based Method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market-risk factors and aggregation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.bis.org/basel_framework/chapter/MAR/21.htm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Independent Challenge, Override and Closure Log</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reviewer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Challenge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner response</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Closure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source, Transformation, Ownership and Refresh Map</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cadence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System / provider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As-of</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Downstream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prices and curves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intraday/daily</t>
+  </si>
+  <si>
+    <t xml:space="preserve">source and interpolation control</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TO MAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">security and lot reconciliation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">model governance evidence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">per release</t>
+  </si>
+  <si>
+    <t xml:space="preserve">version, reviewer, sign-off and change log</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decision-use snapshot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">per decision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">immutable as-of date and source receipt</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pricing and Risk Assumptions</t>
   </si>
   <si>
@@ -444,9 +755,6 @@
     <t xml:space="preserve">Check</t>
   </si>
   <si>
-    <t xml:space="preserve">Status</t>
-  </si>
-  <si>
     <t xml:space="preserve">Price positive</t>
   </si>
   <si>
@@ -480,9 +788,6 @@
     <t xml:space="preserve">Source URL or document</t>
   </si>
   <si>
-    <t xml:space="preserve">As-of</t>
-  </si>
-  <si>
     <t xml:space="preserve">Notes / transformation</t>
   </si>
   <si>
@@ -544,9 +849,6 @@
   </si>
   <si>
     <t xml:space="preserve">Refresh Log</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date</t>
   </si>
   <si>
     <t xml:space="preserve">Trigger</t>
@@ -592,7 +894,7 @@
     <numFmt numFmtId="172" formatCode="0.000000"/>
     <numFmt numFmtId="173" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -669,8 +971,31 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="15"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -680,7 +1005,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E78"/>
-        <bgColor rgb="FF003366"/>
+        <bgColor rgb="FF17365D"/>
       </patternFill>
     </fill>
     <fill>
@@ -695,8 +1020,20 @@
         <bgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF17365D"/>
+        <bgColor rgb="FF333333"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAF7"/>
+        <bgColor rgb="FFE2F0D9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -710,6 +1047,15 @@
       <top/>
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFB7B7B7"/>
       </bottom>
       <diagonal/>
     </border>
@@ -748,7 +1094,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="40">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -786,6 +1132,30 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -857,15 +1227,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -938,11 +1308,11 @@
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFF2CC"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFD9EAF7"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFB7B7B7"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -967,7 +1337,7 @@
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF17365D"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF111827"/>
       <rgbColor rgb="FF333300"/>
@@ -1301,6 +1671,666 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="B2:G12"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="18"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="1" t="str">
+        <f aca="false">Portfolio!B5</f>
+        <v>2Y Treasury</v>
+      </c>
+      <c r="C5" s="29" t="n">
+        <f aca="false">Portfolio!C5*Portfolio!D5</f>
+        <v>1.35</v>
+      </c>
+      <c r="D5" s="29" t="n">
+        <f aca="false">Portfolio!C5*Assumptions!E13</f>
+        <v>1.8</v>
+      </c>
+      <c r="E5" s="20" t="n">
+        <f aca="false">MAX(0,Portfolio!E5-0.002)</f>
+        <v>0.042</v>
+      </c>
+      <c r="F5" s="29" t="n">
+        <f aca="false">Portfolio!C5*Portfolio!I5*(Portfolio!E5-E5)</f>
+        <v>0.113601892879876</v>
+      </c>
+      <c r="G5" s="29" t="n">
+        <f aca="false">C5-D5+F5</f>
+        <v>-0.336398107120124</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="1" t="str">
+        <f aca="false">Portfolio!B6</f>
+        <v>5Y Treasury</v>
+      </c>
+      <c r="C6" s="29" t="n">
+        <f aca="false">Portfolio!C6*Portfolio!D6</f>
+        <v>1.72</v>
+      </c>
+      <c r="D6" s="29" t="n">
+        <f aca="false">Portfolio!C6*Assumptions!E13</f>
+        <v>2.4</v>
+      </c>
+      <c r="E6" s="20" t="n">
+        <f aca="false">MAX(0,Portfolio!E6-0.002)</f>
+        <v>0.043</v>
+      </c>
+      <c r="F6" s="29" t="n">
+        <f aca="false">Portfolio!C6*Portfolio!I6*(Portfolio!E6-E6)</f>
+        <v>0.355960666753355</v>
+      </c>
+      <c r="G6" s="29" t="n">
+        <f aca="false">C6-D6+F6</f>
+        <v>-0.324039333246645</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="1" t="str">
+        <f aca="false">Portfolio!B7</f>
+        <v>10Y Treasury</v>
+      </c>
+      <c r="C7" s="29" t="n">
+        <f aca="false">Portfolio!C7*Portfolio!D7</f>
+        <v>2.5</v>
+      </c>
+      <c r="D7" s="29" t="n">
+        <f aca="false">Portfolio!C7*Assumptions!E13</f>
+        <v>3</v>
+      </c>
+      <c r="E7" s="20" t="n">
+        <f aca="false">MAX(0,Portfolio!E7-0.002)</f>
+        <v>0.053</v>
+      </c>
+      <c r="F7" s="29" t="n">
+        <f aca="false">Portfolio!C7*Portfolio!I7*(Portfolio!E7-E7)</f>
+        <v>0.773001387093704</v>
+      </c>
+      <c r="G7" s="29" t="n">
+        <f aca="false">C7-D7+F7</f>
+        <v>0.273001387093704</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="1" t="str">
+        <f aca="false">Portfolio!B8</f>
+        <v>IG Corporate</v>
+      </c>
+      <c r="C8" s="29" t="n">
+        <f aca="false">Portfolio!C8*Portfolio!D8</f>
+        <v>2.7</v>
+      </c>
+      <c r="D8" s="29" t="n">
+        <f aca="false">Portfolio!C8*Assumptions!E13</f>
+        <v>2.7</v>
+      </c>
+      <c r="E8" s="20" t="n">
+        <f aca="false">MAX(0,Portfolio!E8-0.002)</f>
+        <v>0.066</v>
+      </c>
+      <c r="F8" s="29" t="n">
+        <f aca="false">Portfolio!C8*Portfolio!I8*(Portfolio!E8-E8)</f>
+        <v>0.503563471278034</v>
+      </c>
+      <c r="G8" s="29" t="n">
+        <f aca="false">C8-D8+F8</f>
+        <v>0.503563471278034</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="1" t="str">
+        <f aca="false">Portfolio!B9</f>
+        <v>HY Corporate</v>
+      </c>
+      <c r="C9" s="29" t="n">
+        <f aca="false">Portfolio!C9*Portfolio!D9</f>
+        <v>2.125</v>
+      </c>
+      <c r="D9" s="29" t="n">
+        <f aca="false">Portfolio!C9*Assumptions!E13</f>
+        <v>1.5</v>
+      </c>
+      <c r="E9" s="20" t="n">
+        <f aca="false">MAX(0,Portfolio!E9-0.002)</f>
+        <v>0.103</v>
+      </c>
+      <c r="F9" s="29" t="n">
+        <f aca="false">Portfolio!C9*Portfolio!I9*(Portfolio!E9-E9)</f>
+        <v>0.196507436516471</v>
+      </c>
+      <c r="G9" s="29" t="n">
+        <f aca="false">C9-D9+F9</f>
+        <v>0.821507436516471</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="1" t="str">
+        <f aca="false">Portfolio!B10</f>
+        <v>Municipal</v>
+      </c>
+      <c r="C10" s="29" t="n">
+        <f aca="false">Portfolio!C10*Portfolio!D10</f>
+        <v>0.8</v>
+      </c>
+      <c r="D10" s="29" t="n">
+        <f aca="false">Portfolio!C10*Assumptions!E13</f>
+        <v>1.2</v>
+      </c>
+      <c r="E10" s="20" t="n">
+        <f aca="false">MAX(0,Portfolio!E10-0.002)</f>
+        <v>0.044</v>
+      </c>
+      <c r="F10" s="29" t="n">
+        <f aca="false">Portfolio!C10*Portfolio!I10*(Portfolio!E10-E10)</f>
+        <v>0.374006054263371</v>
+      </c>
+      <c r="G10" s="29" t="n">
+        <f aca="false">C10-D10+F10</f>
+        <v>-0.0259939457366291</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="33" t="s">
+        <v>206</v>
+      </c>
+      <c r="C12" s="34" t="n">
+        <f aca="false">SUM(C5:C10)</f>
+        <v>11.195</v>
+      </c>
+      <c r="D12" s="34" t="n">
+        <f aca="false">SUM(D5:D10)</f>
+        <v>12.6</v>
+      </c>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34" t="n">
+        <f aca="false">SUM(F5:F10)</f>
+        <v>2.31664090878481</v>
+      </c>
+      <c r="G12" s="34" t="n">
+        <f aca="false">SUM(G5:G10)</f>
+        <v>0.911640908784811</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:G2"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:I10"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="18"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C5" s="19" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E5" s="19" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G5" s="19" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H5" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="29" t="n">
+        <f aca="false">-SUMPRODUCT('Key Rate Risk'!C12:G12,C5:G5)/0.0001-SUMPRODUCT(Portfolio!C5:C10,Portfolio!G5:G10)*H5</f>
+        <v>-21.4917592680388</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C6" s="19" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="D6" s="19" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E6" s="19" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F6" s="19" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G6" s="19" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="H6" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="29" t="n">
+        <f aca="false">-SUMPRODUCT('Key Rate Risk'!C12:G12,C6:G6)/0.0001-SUMPRODUCT(Portfolio!C5:C10,Portfolio!G5:G10)*H6</f>
+        <v>21.4917592680388</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="F7" s="19" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G7" s="19" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="H7" s="19" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="I7" s="29" t="n">
+        <f aca="false">-SUMPRODUCT('Key Rate Risk'!C12:G12,C7:G7)/0.0001-SUMPRODUCT(Portfolio!C5:C10,Portfolio!G5:G10)*H7</f>
+        <v>-27.8556112567415</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C8" s="19" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="D8" s="19" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E8" s="19" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="F8" s="19" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="G8" s="19" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="H8" s="19" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="I8" s="29" t="n">
+        <f aca="false">-SUMPRODUCT('Key Rate Risk'!C12:G12,C8:G8)/0.0001-SUMPRODUCT(Portfolio!C5:C10,Portfolio!G5:G10)*H8</f>
+        <v>16.9399006310642</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C9" s="19" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="I9" s="29" t="n">
+        <f aca="false">-SUMPRODUCT('Key Rate Risk'!C12:G12,C9:G9)/0.0001-SUMPRODUCT(Portfolio!C5:C10,Portfolio!G5:G10)*H9</f>
+        <v>-16.2011023062061</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C10" s="19" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I10" s="29" t="n">
+        <f aca="false">-SUMPRODUCT('Key Rate Risk'!C12:G12,C10:G10)/0.0001-SUMPRODUCT(Portfolio!C5:C10,Portfolio!G5:G10)*H10</f>
+        <v>12.6273932949971</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:H2"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:F15"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="38"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="16" t="s">
+        <v>218</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>221</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C5" s="29" t="n">
+        <f aca="false">'Carry &amp; Roll'!C12-'Carry &amp; Roll'!D12</f>
+        <v>-1.405</v>
+      </c>
+      <c r="D5" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="29" t="n">
+        <f aca="false">C5*D5</f>
+        <v>-1.405</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C6" s="29" t="n">
+        <f aca="false">'Carry &amp; Roll'!F12</f>
+        <v>2.31664090878481</v>
+      </c>
+      <c r="D6" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="29" t="n">
+        <f aca="false">C6*D6</f>
+        <v>2.31664090878481</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C7" s="29" t="n">
+        <f aca="false">-Portfolio!K12/0.0001</f>
+        <v>-1158.3204543924</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="E7" s="29" t="n">
+        <f aca="false">C7*D7</f>
+        <v>-0.579160227196202</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C8" s="29" t="n">
+        <f aca="false">-('Key Rate Risk'!C12*0.0002+'Key Rate Risk'!D12*0.0001-'Key Rate Risk'!F12*0.0001)/0.0001</f>
+        <v>-0.00953109863953586</v>
+      </c>
+      <c r="D8" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="29" t="n">
+        <f aca="false">C8*D8</f>
+        <v>-0.00953109863953586</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C9" s="29" t="n">
+        <f aca="false">-SUMPRODUCT(Portfolio!C5:C10,Portfolio!G5:G10)</f>
+        <v>-492.5</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="E9" s="29" t="n">
+        <f aca="false">C9*D9</f>
+        <v>-0.73875</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C10" s="29" t="n">
+        <f aca="false">0.5*SUMPRODUCT(Portfolio!C5:C10,Portfolio!J5:J10)</f>
+        <v>4496.45840799893</v>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>2.5E-007</v>
+      </c>
+      <c r="E10" s="29" t="n">
+        <f aca="false">C10*D10</f>
+        <v>0.00112411460199973</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E13" s="29" t="n">
+        <f aca="false">SUM(E5:E10)</f>
+        <v>-0.414676302448925</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E14" s="28" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E15" s="29" t="n">
+        <f aca="false">E14-E13</f>
+        <v>1.61467630244892</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:F2"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="B2:C12"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -1311,21 +2341,21 @@
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>135</v>
+        <v>236</v>
       </c>
       <c r="C2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>137</v>
+      <c r="B4" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
-        <v>138</v>
+        <v>238</v>
       </c>
       <c r="C5" s="1" t="str">
         <f aca="false">IF('Bond Analytics'!C5&gt;0,"PASS","FAIL")</f>
@@ -1334,7 +2364,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="1" t="s">
-        <v>139</v>
+        <v>239</v>
       </c>
       <c r="C6" s="1" t="str">
         <f aca="false">IF('Bond Analytics'!C6&lt;'Bond Analytics'!C5,"PASS","FAIL")</f>
@@ -1343,7 +2373,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="1" t="s">
-        <v>140</v>
+        <v>240</v>
       </c>
       <c r="C7" s="1" t="str">
         <f aca="false">IF('Bond Analytics'!C8&gt;0,"PASS","FAIL")</f>
@@ -1352,7 +2382,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="1" t="s">
-        <v>141</v>
+        <v>241</v>
       </c>
       <c r="C8" s="1" t="str">
         <f aca="false">IF('Bond Analytics'!C9&gt;0,"PASS","FAIL")</f>
@@ -1361,7 +2391,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
-        <v>142</v>
+        <v>242</v>
       </c>
       <c r="C9" s="1" t="str">
         <f aca="false">IF(ABS('Key Rate Risk'!H12-Portfolio!K12)&lt;0.1,"PASS","REVIEW")</f>
@@ -1370,7 +2400,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="1" t="s">
-        <v>143</v>
+        <v>243</v>
       </c>
       <c r="C10" s="1" t="str">
         <f aca="false">IF(MAX('Zero Curve'!F6:F14-'Zero Curve'!F5:F13)&lt;=0,"PASS","REVIEW")</f>
@@ -1379,7 +2409,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>144</v>
+        <v>244</v>
       </c>
       <c r="C11" s="1" t="str">
         <f aca="false">IF(COUNT('P&amp;L Explain'!E5:E10)=6,"PASS","FAIL")</f>
@@ -1388,7 +2418,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="1" t="s">
-        <v>145</v>
+        <v>245</v>
       </c>
       <c r="C12" s="1" t="str">
         <f aca="false">IF(COUNTIF(C5:C11,"FAIL")=0,"PASS","FAIL")</f>
@@ -1423,7 +2453,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -1440,108 +2470,108 @@
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>146</v>
+        <v>246</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>150</v>
+      <c r="B4" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>248</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="31" t="s">
-        <v>151</v>
-      </c>
-      <c r="C5" s="31" t="s">
-        <v>152</v>
-      </c>
-      <c r="D5" s="31" t="s">
+      <c r="B5" s="37" t="s">
+        <v>250</v>
+      </c>
+      <c r="C5" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="D5" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="31" t="s">
-        <v>153</v>
+      <c r="E5" s="37" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="C6" s="31" t="s">
-        <v>155</v>
-      </c>
-      <c r="D6" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="E6" s="31" t="s">
-        <v>157</v>
+      <c r="B6" s="37" t="s">
+        <v>253</v>
+      </c>
+      <c r="C6" s="37" t="s">
+        <v>254</v>
+      </c>
+      <c r="D6" s="37" t="s">
+        <v>255</v>
+      </c>
+      <c r="E6" s="37" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="31" t="s">
-        <v>158</v>
-      </c>
-      <c r="C7" s="31" t="s">
-        <v>159</v>
-      </c>
-      <c r="D7" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="E7" s="31" t="s">
-        <v>160</v>
+      <c r="B7" s="37" t="s">
+        <v>257</v>
+      </c>
+      <c r="C7" s="37" t="s">
+        <v>258</v>
+      </c>
+      <c r="D7" s="37" t="s">
+        <v>255</v>
+      </c>
+      <c r="E7" s="37" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="C8" s="31" t="s">
-        <v>162</v>
-      </c>
-      <c r="D8" s="31" t="s">
+      <c r="B8" s="37" t="s">
+        <v>260</v>
+      </c>
+      <c r="C8" s="37" t="s">
+        <v>261</v>
+      </c>
+      <c r="D8" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="31" t="s">
-        <v>163</v>
+      <c r="E8" s="37" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="31" t="s">
-        <v>164</v>
-      </c>
-      <c r="C9" s="31" t="s">
-        <v>165</v>
-      </c>
-      <c r="D9" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="E9" s="31" t="s">
-        <v>166</v>
+      <c r="B9" s="37" t="s">
+        <v>263</v>
+      </c>
+      <c r="C9" s="37" t="s">
+        <v>264</v>
+      </c>
+      <c r="D9" s="37" t="s">
+        <v>255</v>
+      </c>
+      <c r="E9" s="37" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="32" t="s">
-        <v>167</v>
-      </c>
-      <c r="C10" s="32" t="s">
-        <v>168</v>
-      </c>
-      <c r="D10" s="32" t="s">
+      <c r="B10" s="38" t="s">
+        <v>266</v>
+      </c>
+      <c r="C10" s="38" t="s">
+        <v>267</v>
+      </c>
+      <c r="D10" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="32" t="s">
-        <v>169</v>
+      <c r="E10" s="38" t="s">
+        <v>268</v>
       </c>
     </row>
   </sheetData>
@@ -1558,7 +2588,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -1577,7 +2607,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>170</v>
+        <v>269</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -1586,236 +2616,236 @@
       <c r="G2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>176</v>
+      <c r="B4" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>270</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>273</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="33" t="s">
-        <v>177</v>
-      </c>
-      <c r="D5" s="33" t="s">
-        <v>168</v>
-      </c>
-      <c r="E5" s="33" t="s">
-        <v>178</v>
-      </c>
-      <c r="F5" s="33" t="s">
-        <v>179</v>
-      </c>
-      <c r="G5" s="33" t="s">
-        <v>180</v>
+      <c r="C5" s="39" t="s">
+        <v>275</v>
+      </c>
+      <c r="D5" s="39" t="s">
+        <v>267</v>
+      </c>
+      <c r="E5" s="39" t="s">
+        <v>276</v>
+      </c>
+      <c r="F5" s="39" t="s">
+        <v>277</v>
+      </c>
+      <c r="G5" s="39" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="33"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="33"/>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="33"/>
-      <c r="G7" s="33"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="39"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="33"/>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="39"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="33"/>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="33"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="33"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="33"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="39"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="33"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="33"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="33"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="33"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="33"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="33"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="33"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="33"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="33"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="33"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="33"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="33"/>
-      <c r="C21" s="33"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="33"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="33"/>
-      <c r="C22" s="33"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="33"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="33"/>
-      <c r="C23" s="33"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="33"/>
-      <c r="G23" s="33"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="39"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="33"/>
-      <c r="C24" s="33"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="33"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="33"/>
-      <c r="C25" s="33"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="33"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="39"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="33"/>
-      <c r="C26" s="33"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="33"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="39"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="39"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="33"/>
-      <c r="C27" s="33"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="33"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="39"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="33"/>
-      <c r="C28" s="33"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="33"/>
-      <c r="G28" s="33"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="39"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="33"/>
-      <c r="C29" s="33"/>
-      <c r="D29" s="33"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="33"/>
-      <c r="G29" s="33"/>
+      <c r="B29" s="39"/>
+      <c r="C29" s="39"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="39"/>
+      <c r="G29" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1836,6 +2866,1085 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="B2:F64"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F29" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F37" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C44" s="13"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="13"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C45" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D45" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E45" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F45" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C52" s="13"/>
+      <c r="D52" s="13"/>
+      <c r="E52" s="13"/>
+      <c r="F52" s="13"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C53" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D53" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E53" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F53" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B58" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B60" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C60" s="13"/>
+      <c r="D60" s="13"/>
+      <c r="E60" s="13"/>
+      <c r="F60" s="13"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="C61" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="D61" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="E61" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="F61" s="14" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B62" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F62" s="1"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F63" s="1"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B64" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F64" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B60:F60"/>
+  </mergeCells>
+  <dataValidations count="6">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F14:F18" type="list">
+      <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F22:F26" type="list">
+      <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F30:F34" type="list">
+      <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F38:F42" type="list">
+      <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F46:F50" type="list">
+      <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F54:F58" type="list">
+      <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:I9"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:I2"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H5:H54" type="list">
+      <formula1>"OPEN,IN REVIEW,REMEDIATED,ACCEPTED RISK,CLOSED"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G5:G54" type="list">
+      <formula1>"LOW,MEDIUM,HIGH,CRITICAL"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:J8"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="J4" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="15" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="15" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="15" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="15" t="s">
+        <v>116</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:J2"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J5:J40" type="list">
+      <formula1>"TO MAP,ACTIVE,STALE,EXCEPTION,RETIRED"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="B2:F14"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -1847,7 +3956,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>24</v>
+        <v>125</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -1855,200 +3964,200 @@
       <c r="F2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="10" t="s">
+      <c r="B4" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="D4" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>28</v>
+      <c r="E4" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="11" t="n">
+        <v>130</v>
+      </c>
+      <c r="C5" s="17" t="n">
         <v>1000</v>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="17" t="n">
         <v>1000</v>
       </c>
-      <c r="E5" s="12" t="n">
+      <c r="E5" s="18" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D5,C5)</f>
         <v>1000</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>30</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="13" t="n">
+        <v>132</v>
+      </c>
+      <c r="C6" s="19" t="n">
         <v>0.05</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="19" t="n">
         <v>0.05</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="20" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D6,C6)</f>
         <v>0.05</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="13" t="n">
+        <v>134</v>
+      </c>
+      <c r="C7" s="19" t="n">
         <v>0.055</v>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="21" t="n">
         <v>0.085</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="20" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D7,C7)</f>
         <v>0.085</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="16" t="n">
+        <v>135</v>
+      </c>
+      <c r="C8" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="E8" s="23" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D8,C8)</f>
         <v>10</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>35</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="18" t="n">
+        <v>137</v>
+      </c>
+      <c r="C9" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="D9" s="18" t="n">
+      <c r="D9" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="E9" s="19" t="n">
+      <c r="E9" s="25" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D9,C9)</f>
         <v>2</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>37</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="13" t="n">
+        <v>139</v>
+      </c>
+      <c r="C10" s="19" t="n">
         <v>0.01</v>
       </c>
-      <c r="D10" s="15" t="n">
+      <c r="D10" s="21" t="n">
         <v>0.025</v>
       </c>
-      <c r="E10" s="14" t="n">
+      <c r="E10" s="20" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D10,C10)</f>
         <v>0.025</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="20" t="n">
+        <v>140</v>
+      </c>
+      <c r="C11" s="26" t="n">
         <v>0.0001</v>
       </c>
-      <c r="D11" s="20" t="n">
+      <c r="D11" s="26" t="n">
         <v>0.0001</v>
       </c>
-      <c r="E11" s="21" t="n">
+      <c r="E11" s="27" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D11,C11)</f>
         <v>0.0001</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" s="16" t="n">
+        <v>141</v>
+      </c>
+      <c r="C12" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="17" t="n">
+      <c r="E12" s="23" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D12,C12)</f>
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>35</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" s="13" t="n">
+        <v>142</v>
+      </c>
+      <c r="C13" s="19" t="n">
         <v>0.045</v>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="19" t="n">
         <v>0.06</v>
       </c>
-      <c r="E13" s="14" t="n">
+      <c r="E13" s="20" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D13,C13)</f>
         <v>0.06</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="22" t="n">
+        <v>143</v>
+      </c>
+      <c r="C14" s="28" t="n">
         <v>50</v>
       </c>
-      <c r="D14" s="22" t="n">
+      <c r="D14" s="28" t="n">
         <v>50</v>
       </c>
-      <c r="E14" s="23" t="n">
+      <c r="E14" s="29" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D14,C14)</f>
         <v>50</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>43</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -2065,7 +4174,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -2082,7 +4191,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>44</v>
+        <v>145</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -2091,251 +4200,251 @@
       <c r="G2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>50</v>
+      <c r="B4" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="24" t="n">
+      <c r="B5" s="30" t="n">
         <v>0.25</v>
       </c>
-      <c r="C5" s="13" t="n">
+      <c r="C5" s="19" t="n">
         <v>0.048</v>
       </c>
-      <c r="D5" s="13" t="n">
+      <c r="D5" s="19" t="n">
         <v>0.053</v>
       </c>
-      <c r="E5" s="14" t="n">
+      <c r="E5" s="20" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D5,C5)</f>
         <v>0.053</v>
       </c>
-      <c r="F5" s="25" t="n">
+      <c r="F5" s="31" t="n">
         <f aca="false">EXP(-E5*B5)</f>
         <v>0.986837394830341</v>
       </c>
-      <c r="G5" s="14" t="n">
+      <c r="G5" s="20" t="n">
         <f aca="false">E5</f>
         <v>0.053</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="24" t="n">
+      <c r="B6" s="30" t="n">
         <v>0.5</v>
       </c>
-      <c r="C6" s="13" t="n">
+      <c r="C6" s="19" t="n">
         <v>0.047</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="19" t="n">
         <v>0.052</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="20" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D6,C6)</f>
         <v>0.052</v>
       </c>
-      <c r="F6" s="25" t="n">
+      <c r="F6" s="31" t="n">
         <f aca="false">EXP(-E6*B6)</f>
         <v>0.974335089608749</v>
       </c>
-      <c r="G6" s="14" t="n">
+      <c r="G6" s="20" t="n">
         <f aca="false">IFERROR(-LN(F6/F5)/(B6-B5),0)</f>
         <v>0.051</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="24" t="n">
+      <c r="B7" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="13" t="n">
+      <c r="C7" s="19" t="n">
         <v>0.045</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="19" t="n">
         <v>0.05</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="20" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D7,C7)</f>
         <v>0.05</v>
       </c>
-      <c r="F7" s="25" t="n">
+      <c r="F7" s="31" t="n">
         <f aca="false">EXP(-E7*B7)</f>
         <v>0.951229424500714</v>
       </c>
-      <c r="G7" s="14" t="n">
+      <c r="G7" s="20" t="n">
         <f aca="false">IFERROR(-LN(F7/F6)/(B7-B6),0)</f>
         <v>0.048</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="24" t="n">
+      <c r="B8" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C8" s="19" t="n">
         <v>0.043</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="19" t="n">
         <v>0.048</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="20" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D8,C8)</f>
         <v>0.048</v>
       </c>
-      <c r="F8" s="25" t="n">
+      <c r="F8" s="31" t="n">
         <f aca="false">EXP(-E8*B8)</f>
         <v>0.908464016068706</v>
       </c>
-      <c r="G8" s="14" t="n">
+      <c r="G8" s="20" t="n">
         <f aca="false">IFERROR(-LN(F8/F7)/(B8-B7),0)</f>
         <v>0.0459999999999999</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="24" t="n">
+      <c r="B9" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="19" t="n">
         <v>0.042</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="19" t="n">
         <v>0.047</v>
       </c>
-      <c r="E9" s="14" t="n">
+      <c r="E9" s="20" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D9,C9)</f>
         <v>0.047</v>
       </c>
-      <c r="F9" s="25" t="n">
+      <c r="F9" s="31" t="n">
         <f aca="false">EXP(-E9*B9)</f>
         <v>0.868489311697668</v>
       </c>
-      <c r="G9" s="14" t="n">
+      <c r="G9" s="20" t="n">
         <f aca="false">IFERROR(-LN(F9/F8)/(B9-B8),0)</f>
         <v>0.0450000000000001</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="24" t="n">
+      <c r="B10" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="C10" s="13" t="n">
+      <c r="C10" s="19" t="n">
         <v>0.043</v>
       </c>
-      <c r="D10" s="15" t="n">
+      <c r="D10" s="21" t="n">
         <v>0.08</v>
       </c>
-      <c r="E10" s="14" t="n">
+      <c r="E10" s="20" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D10,C10)</f>
         <v>0.08</v>
       </c>
-      <c r="F10" s="25" t="n">
+      <c r="F10" s="31" t="n">
         <f aca="false">EXP(-E10*B10)</f>
         <v>0.670320046035639</v>
       </c>
-      <c r="G10" s="14" t="n">
+      <c r="G10" s="20" t="n">
         <f aca="false">IFERROR(-LN(F10/F9)/(B10-B9),0)</f>
         <v>0.1295</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="24" t="n">
+      <c r="B11" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="C11" s="13" t="n">
+      <c r="C11" s="19" t="n">
         <v>0.045</v>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="19" t="n">
         <v>0.057</v>
       </c>
-      <c r="E11" s="14" t="n">
+      <c r="E11" s="20" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D11,C11)</f>
         <v>0.057</v>
       </c>
-      <c r="F11" s="25" t="n">
+      <c r="F11" s="31" t="n">
         <f aca="false">EXP(-E11*B11)</f>
         <v>0.670990701353446</v>
       </c>
-      <c r="G11" s="14" t="n">
+      <c r="G11" s="20" t="n">
         <f aca="false">IFERROR(-LN(F11/F10)/(B11-B10),0)</f>
         <v>-0.000499999999999911</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="24" t="n">
+      <c r="B12" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="13" t="n">
+      <c r="C12" s="19" t="n">
         <v>0.047</v>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="19" t="n">
         <v>0.059</v>
       </c>
-      <c r="E12" s="14" t="n">
+      <c r="E12" s="20" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D12,C12)</f>
         <v>0.059</v>
       </c>
-      <c r="F12" s="25" t="n">
+      <c r="F12" s="31" t="n">
         <f aca="false">EXP(-E12*B12)</f>
         <v>0.554327284734507</v>
       </c>
-      <c r="G12" s="14" t="n">
+      <c r="G12" s="20" t="n">
         <f aca="false">IFERROR(-LN(F12/F11)/(B12-B11),0)</f>
         <v>0.0636666666666666</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="24" t="n">
+      <c r="B13" s="30" t="n">
         <v>20</v>
       </c>
-      <c r="C13" s="13" t="n">
+      <c r="C13" s="19" t="n">
         <v>0.049</v>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="19" t="n">
         <v>0.061</v>
       </c>
-      <c r="E13" s="14" t="n">
+      <c r="E13" s="20" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D13,C13)</f>
         <v>0.061</v>
       </c>
-      <c r="F13" s="25" t="n">
+      <c r="F13" s="31" t="n">
         <f aca="false">EXP(-E13*B13)</f>
         <v>0.295230166924014</v>
       </c>
-      <c r="G13" s="14" t="n">
+      <c r="G13" s="20" t="n">
         <f aca="false">IFERROR(-LN(F13/F12)/(B13-B12),0)</f>
         <v>0.063</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="24" t="n">
+      <c r="B14" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="C14" s="13" t="n">
+      <c r="C14" s="19" t="n">
         <v>0.05</v>
       </c>
-      <c r="D14" s="15" t="n">
+      <c r="D14" s="21" t="n">
         <v>0.09</v>
       </c>
-      <c r="E14" s="14" t="n">
+      <c r="E14" s="20" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D14,C14)</f>
         <v>0.09</v>
       </c>
-      <c r="F14" s="25" t="n">
+      <c r="F14" s="31" t="n">
         <f aca="false">EXP(-E14*B14)</f>
         <v>0.0672055127397498</v>
       </c>
-      <c r="G14" s="14" t="n">
+      <c r="G14" s="20" t="n">
         <f aca="false">IFERROR(-LN(F14/F13)/(B14-B13),0)</f>
         <v>0.148</v>
       </c>
@@ -2354,7 +4463,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -2371,174 +4480,174 @@
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>51</v>
+        <v>152</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>55</v>
+      <c r="B4" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C5" s="12" t="n">
+        <v>157</v>
+      </c>
+      <c r="C5" s="18" t="n">
         <f aca="false">-PV(Assumptions!E7/Assumptions!E9,Assumptions!E8*Assumptions!E9,Assumptions!E5*Assumptions!E6/Assumptions!E9,Assumptions!E5)</f>
         <v>767.348598356452</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>30</v>
+        <v>131</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>57</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C6" s="12" t="n">
+        <v>159</v>
+      </c>
+      <c r="C6" s="18" t="n">
         <f aca="false">-PV((Assumptions!E7+Assumptions!E11)/Assumptions!E9,Assumptions!E8*Assumptions!E9,Assumptions!E5*Assumptions!E6/Assumptions!E9,Assumptions!E5)</f>
         <v>766.786033965729</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>30</v>
+        <v>131</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>59</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="12" t="n">
+        <v>161</v>
+      </c>
+      <c r="C7" s="18" t="n">
         <f aca="false">-PV((Assumptions!E7-Assumptions!E11)/Assumptions!E9,Assumptions!E8*Assumptions!E9,Assumptions!E5*Assumptions!E6/Assumptions!E9,Assumptions!E5)</f>
         <v>767.911678302859</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>30</v>
+        <v>131</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>59</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C8" s="26" t="n">
+        <v>162</v>
+      </c>
+      <c r="C8" s="32" t="n">
         <f aca="false">IFERROR((C7-C6)/(2*C5*Assumptions!E11),0)</f>
         <v>7.33463473798651</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>35</v>
+        <v>136</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>62</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" s="26" t="n">
+        <v>164</v>
+      </c>
+      <c r="C9" s="32" t="n">
         <f aca="false">IFERROR((C6+C7-2*C5)/(C5*Assumptions!E11^2),0)</f>
         <v>67.1866327698296</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>64</v>
+        <v>165</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>65</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" s="12" t="n">
+        <v>167</v>
+      </c>
+      <c r="C10" s="18" t="n">
         <f aca="false">(C7-C6)/2</f>
         <v>0.562822168565049</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>30</v>
+        <v>131</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>67</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" s="14" t="n">
+        <v>169</v>
+      </c>
+      <c r="C11" s="20" t="n">
         <f aca="false">Assumptions!E5*Assumptions!E6/C5</f>
         <v>0.0651594335444056</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>69</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" s="12" t="n">
+        <v>171</v>
+      </c>
+      <c r="C12" s="18" t="n">
         <f aca="false">-PV((Assumptions!E7+Assumptions!E10)/Assumptions!E9,Assumptions!E8*Assumptions!E9,Assumptions!E5*Assumptions!E6/Assumptions!E9,Assumptions!E5)</f>
         <v>641.488525452151</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>30</v>
+        <v>131</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>71</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" s="12" t="n">
+        <v>173</v>
+      </c>
+      <c r="C13" s="18" t="n">
         <f aca="false">C5*(1-C8*Assumptions!E10+0.5*C9*Assumptions!E10^2)</f>
         <v>642.754171366508</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>30</v>
+        <v>131</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>73</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C14" s="12" t="n">
+        <v>175</v>
+      </c>
+      <c r="C14" s="18" t="n">
         <f aca="false">C12-C13</f>
         <v>-1.26564591435636</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>30</v>
+        <v>131</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>75</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -2555,7 +4664,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -2573,7 +4682,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>76</v>
+        <v>177</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -2586,1027 +4695,292 @@
       <c r="K2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="K4" s="10" t="s">
-        <v>66</v>
+      <c r="B4" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="J4" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="K4" s="16" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="C5" s="22" t="n">
+      <c r="B5" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="C5" s="28" t="n">
         <v>30</v>
       </c>
-      <c r="D5" s="13" t="n">
+      <c r="D5" s="19" t="n">
         <v>0.045</v>
       </c>
-      <c r="E5" s="13" t="n">
+      <c r="E5" s="19" t="n">
         <v>0.044</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="G5" s="16" t="n">
+      <c r="G5" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="12" t="n">
+      <c r="H5" s="18" t="n">
         <f aca="false">-PV(E5/2,F5*2,100*D5/2,100)</f>
         <v>100.189466000932</v>
       </c>
-      <c r="I5" s="26" t="n">
+      <c r="I5" s="32" t="n">
         <f aca="false">IFERROR(((-PV((E5-0.0001)/2,F5*2,100*D5/2,100))-(-PV((E5+0.0001)/2,F5*2,100*D5/2,100)))/(2*H5*0.0001),0)</f>
         <v>1.89336488133126</v>
       </c>
-      <c r="J5" s="26" t="n">
+      <c r="J5" s="32" t="n">
         <f aca="false">IFERROR(((-PV((E5+0.0001)/2,F5*2,100*D5/2,100))+(-PV((E5-0.0001)/2,F5*2,100*D5/2,100))-2*H5)/(H5*0.0001^2),0)</f>
         <v>4.58004825211457</v>
       </c>
-      <c r="K5" s="23" t="n">
+      <c r="K5" s="29" t="n">
         <f aca="false">C5*I5*0.0001</f>
         <v>0.00568009464399378</v>
       </c>
-      <c r="L5" s="26"/>
+      <c r="L5" s="32"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="C6" s="22" t="n">
+      <c r="B6" s="22" t="s">
+        <v>186</v>
+      </c>
+      <c r="C6" s="28" t="n">
         <v>40</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="19" t="n">
         <v>0.043</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="19" t="n">
         <v>0.045</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="F6" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="G6" s="16" t="n">
+      <c r="G6" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="12" t="n">
+      <c r="H6" s="18" t="n">
         <f aca="false">-PV(E6/2,F6*2,100*D6/2,100)</f>
         <v>99.1133783651132</v>
       </c>
-      <c r="I6" s="26" t="n">
+      <c r="I6" s="32" t="n">
         <f aca="false">IFERROR(((-PV((E6-0.0001)/2,F6*2,100*D6/2,100))-(-PV((E6+0.0001)/2,F6*2,100*D6/2,100)))/(2*H6*0.0001),0)</f>
         <v>4.44950833441694</v>
       </c>
-      <c r="J6" s="26" t="n">
+      <c r="J6" s="32" t="n">
         <f aca="false">IFERROR(((-PV((E6+0.0001)/2,F6*2,100*D6/2,100))+(-PV((E6-0.0001)/2,F6*2,100*D6/2,100))-2*H6)/(H6*0.0001^2),0)</f>
         <v>23.1671250475456</v>
       </c>
-      <c r="K6" s="23" t="n">
+      <c r="K6" s="29" t="n">
         <f aca="false">C6*I6*0.0001</f>
         <v>0.0177980333376678</v>
       </c>
-      <c r="L6" s="26"/>
+      <c r="L6" s="32"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="C7" s="22" t="n">
+      <c r="B7" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="C7" s="28" t="n">
         <v>50</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="19" t="n">
         <v>0.05</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="19" t="n">
         <v>0.055</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="G7" s="16" t="n">
+      <c r="G7" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="12" t="n">
+      <c r="H7" s="18" t="n">
         <f aca="false">-PV(E7/2,F7*2,100*D7/2,100)</f>
         <v>96.1931869665561</v>
       </c>
-      <c r="I7" s="26" t="n">
+      <c r="I7" s="32" t="n">
         <f aca="false">IFERROR(((-PV((E7-0.0001)/2,F7*2,100*D7/2,100))-(-PV((E7+0.0001)/2,F7*2,100*D7/2,100)))/(2*H7*0.0001),0)</f>
         <v>7.73001387093704</v>
       </c>
-      <c r="J7" s="26" t="n">
+      <c r="J7" s="32" t="n">
         <f aca="false">IFERROR(((-PV((E7+0.0001)/2,F7*2,100*D7/2,100))+(-PV((E7-0.0001)/2,F7*2,100*D7/2,100))-2*H7)/(H7*0.0001^2),0)</f>
         <v>72.7069530960584</v>
       </c>
-      <c r="K7" s="23" t="n">
+      <c r="K7" s="29" t="n">
         <f aca="false">C7*I7*0.0001</f>
         <v>0.0386500693546852</v>
       </c>
-      <c r="L7" s="26"/>
+      <c r="L7" s="32"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="C8" s="22" t="n">
+      <c r="B8" s="22" t="s">
+        <v>188</v>
+      </c>
+      <c r="C8" s="28" t="n">
         <v>45</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="19" t="n">
         <v>0.06</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="19" t="n">
         <v>0.068</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="F8" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="G8" s="16" t="n">
+      <c r="G8" s="22" t="n">
         <v>5.5</v>
       </c>
-      <c r="H8" s="12" t="n">
+      <c r="H8" s="18" t="n">
         <f aca="false">-PV(E8/2,F8*2,100*D8/2,100)</f>
         <v>95.602342663271</v>
       </c>
-      <c r="I8" s="26" t="n">
+      <c r="I8" s="32" t="n">
         <f aca="false">IFERROR(((-PV((E8-0.0001)/2,F8*2,100*D8/2,100))-(-PV((E8+0.0001)/2,F8*2,100*D8/2,100)))/(2*H8*0.0001),0)</f>
         <v>5.59514968086704</v>
       </c>
-      <c r="J8" s="26" t="n">
+      <c r="J8" s="32" t="n">
         <f aca="false">IFERROR(((-PV((E8+0.0001)/2,F8*2,100*D8/2,100))+(-PV((E8-0.0001)/2,F8*2,100*D8/2,100))-2*H8)/(H8*0.0001^2),0)</f>
         <v>37.9276522067983</v>
       </c>
-      <c r="K8" s="23" t="n">
+      <c r="K8" s="29" t="n">
         <f aca="false">C8*I8*0.0001</f>
         <v>0.0251781735639017</v>
       </c>
-      <c r="L8" s="26"/>
+      <c r="L8" s="32"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="C9" s="22" t="n">
+      <c r="B9" s="22" t="s">
+        <v>189</v>
+      </c>
+      <c r="C9" s="28" t="n">
         <v>25</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="19" t="n">
         <v>0.085</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="19" t="n">
         <v>0.105</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F9" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="G9" s="16" t="n">
+      <c r="G9" s="22" t="n">
         <v>3.8</v>
       </c>
-      <c r="H9" s="12" t="n">
+      <c r="H9" s="18" t="n">
         <f aca="false">-PV(E9/2,F9*2,100*D9/2,100)</f>
         <v>92.3711595277973</v>
       </c>
-      <c r="I9" s="26" t="n">
+      <c r="I9" s="32" t="n">
         <f aca="false">IFERROR(((-PV((E9-0.0001)/2,F9*2,100*D9/2,100))-(-PV((E9+0.0001)/2,F9*2,100*D9/2,100)))/(2*H9*0.0001),0)</f>
         <v>3.93014873032941</v>
       </c>
-      <c r="J9" s="26" t="n">
+      <c r="J9" s="32" t="n">
         <f aca="false">IFERROR(((-PV((E9+0.0001)/2,F9*2,100*D9/2,100))+(-PV((E9-0.0001)/2,F9*2,100*D9/2,100))-2*H9)/(H9*0.0001^2),0)</f>
         <v>19.2026958764139</v>
       </c>
-      <c r="K9" s="23" t="n">
+      <c r="K9" s="29" t="n">
         <f aca="false">C9*I9*0.0001</f>
         <v>0.00982537182582354</v>
       </c>
-      <c r="L9" s="26"/>
+      <c r="L9" s="32"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="C10" s="22" t="n">
+      <c r="B10" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="C10" s="28" t="n">
         <v>20</v>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="19" t="n">
         <v>0.04</v>
       </c>
-      <c r="E10" s="13" t="n">
+      <c r="E10" s="19" t="n">
         <v>0.046</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="F10" s="22" t="n">
         <v>12</v>
       </c>
-      <c r="G10" s="16" t="n">
+      <c r="G10" s="22" t="n">
         <v>7.5</v>
       </c>
-      <c r="H10" s="12" t="n">
+      <c r="H10" s="18" t="n">
         <f aca="false">-PV(E10/2,F10*2,100*D10/2,100)</f>
         <v>94.514022674657</v>
       </c>
-      <c r="I10" s="26" t="n">
+      <c r="I10" s="32" t="n">
         <f aca="false">IFERROR(((-PV((E10-0.0001)/2,F10*2,100*D10/2,100))-(-PV((E10+0.0001)/2,F10*2,100*D10/2,100)))/(2*H10*0.0001),0)</f>
         <v>9.35015135658426</v>
       </c>
-      <c r="J10" s="26" t="n">
+      <c r="J10" s="32" t="n">
         <f aca="false">IFERROR(((-PV((E10+0.0001)/2,F10*2,100*D10/2,100))+(-PV((E10-0.0001)/2,F10*2,100*D10/2,100))-2*H10)/(H10*0.0001^2),0)</f>
         <v>105.33354827567</v>
       </c>
-      <c r="K10" s="23" t="n">
+      <c r="K10" s="29" t="n">
         <f aca="false">C10*I10*0.0001</f>
         <v>0.0187003027131685</v>
       </c>
-      <c r="L10" s="26"/>
+      <c r="L10" s="32"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="27" t="s">
-        <v>90</v>
-      </c>
-      <c r="C12" s="28" t="n">
+      <c r="B12" s="33" t="s">
+        <v>191</v>
+      </c>
+      <c r="C12" s="34" t="n">
         <f aca="false">SUM(C5:C10)</f>
         <v>210</v>
       </c>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="29" t="n">
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="35" t="n">
         <f aca="false">SUMPRODUCT(C5:C10,G5:G10)/SUM(C5:C10)</f>
         <v>2.3452380952381</v>
       </c>
-      <c r="H12" s="27"/>
-      <c r="I12" s="29" t="n">
+      <c r="H12" s="33"/>
+      <c r="I12" s="35" t="n">
         <f aca="false">SUMPRODUCT(C5:C10,I5:I10)/SUM(C5:C10)</f>
         <v>5.51581168758288</v>
       </c>
-      <c r="J12" s="29" t="n">
+      <c r="J12" s="35" t="n">
         <f aca="false">SUMPRODUCT(C5:C10,J5:J10)/SUM(C5:C10)</f>
         <v>42.8234134095136</v>
       </c>
-      <c r="K12" s="28" t="n">
+      <c r="K12" s="34" t="n">
         <f aca="false">SUM(K5:K10)</f>
         <v>0.11583204543924</v>
       </c>
-      <c r="L12" s="29"/>
+      <c r="L12" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:K2"/>
-  </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="B2:H12"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="16"/>
-  </cols>
-  <sheetData>
-    <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="str">
-        <f aca="false">Portfolio!B5</f>
-        <v>2Y Treasury</v>
-      </c>
-      <c r="C5" s="23" t="n">
-        <f aca="false">Portfolio!K5*MAX(0,1-ABS(Portfolio!F5-2)/MAX(2,2))</f>
-        <v>0.00568009464399378</v>
-      </c>
-      <c r="D5" s="23" t="n">
-        <f aca="false">Portfolio!K5*MAX(0,1-ABS(Portfolio!F5-5)/MAX(2,5))</f>
-        <v>0.00227203785759751</v>
-      </c>
-      <c r="E5" s="23" t="n">
-        <f aca="false">Portfolio!K5*MAX(0,1-ABS(Portfolio!F5-10)/MAX(2,10))</f>
-        <v>0.00113601892879876</v>
-      </c>
-      <c r="F5" s="23" t="n">
-        <f aca="false">Portfolio!K5*MAX(0,1-ABS(Portfolio!F5-20)/MAX(2,20))</f>
-        <v>0.000568009464399378</v>
-      </c>
-      <c r="G5" s="23" t="n">
-        <f aca="false">Portfolio!K5*MAX(0,1-ABS(Portfolio!F5-30)/MAX(2,30))</f>
-        <v>0.000378672976266252</v>
-      </c>
-      <c r="H5" s="23" t="n">
-        <f aca="false">SUM(C5:G5)</f>
-        <v>0.0100348338710557</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="str">
-        <f aca="false">Portfolio!B6</f>
-        <v>5Y Treasury</v>
-      </c>
-      <c r="C6" s="23" t="n">
-        <f aca="false">Portfolio!K6*MAX(0,1-ABS(Portfolio!F6-2)/MAX(2,2))</f>
-        <v>0</v>
-      </c>
-      <c r="D6" s="23" t="n">
-        <f aca="false">Portfolio!K6*MAX(0,1-ABS(Portfolio!F6-5)/MAX(2,5))</f>
-        <v>0.0177980333376678</v>
-      </c>
-      <c r="E6" s="23" t="n">
-        <f aca="false">Portfolio!K6*MAX(0,1-ABS(Portfolio!F6-10)/MAX(2,10))</f>
-        <v>0.00889901666883388</v>
-      </c>
-      <c r="F6" s="23" t="n">
-        <f aca="false">Portfolio!K6*MAX(0,1-ABS(Portfolio!F6-20)/MAX(2,20))</f>
-        <v>0.00444950833441694</v>
-      </c>
-      <c r="G6" s="23" t="n">
-        <f aca="false">Portfolio!K6*MAX(0,1-ABS(Portfolio!F6-30)/MAX(2,30))</f>
-        <v>0.00296633888961129</v>
-      </c>
-      <c r="H6" s="23" t="n">
-        <f aca="false">SUM(C6:G6)</f>
-        <v>0.0341128972305299</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="str">
-        <f aca="false">Portfolio!B7</f>
-        <v>10Y Treasury</v>
-      </c>
-      <c r="C7" s="23" t="n">
-        <f aca="false">Portfolio!K7*MAX(0,1-ABS(Portfolio!F7-2)/MAX(2,2))</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="23" t="n">
-        <f aca="false">Portfolio!K7*MAX(0,1-ABS(Portfolio!F7-5)/MAX(2,5))</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="23" t="n">
-        <f aca="false">Portfolio!K7*MAX(0,1-ABS(Portfolio!F7-10)/MAX(2,10))</f>
-        <v>0.0386500693546852</v>
-      </c>
-      <c r="F7" s="23" t="n">
-        <f aca="false">Portfolio!K7*MAX(0,1-ABS(Portfolio!F7-20)/MAX(2,20))</f>
-        <v>0.0193250346773426</v>
-      </c>
-      <c r="G7" s="23" t="n">
-        <f aca="false">Portfolio!K7*MAX(0,1-ABS(Portfolio!F7-30)/MAX(2,30))</f>
-        <v>0.0128833564515617</v>
-      </c>
-      <c r="H7" s="23" t="n">
-        <f aca="false">SUM(C7:G7)</f>
-        <v>0.0708584604835895</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="str">
-        <f aca="false">Portfolio!B8</f>
-        <v>IG Corporate</v>
-      </c>
-      <c r="C8" s="23" t="n">
-        <f aca="false">Portfolio!K8*MAX(0,1-ABS(Portfolio!F8-2)/MAX(2,2))</f>
-        <v>0</v>
-      </c>
-      <c r="D8" s="23" t="n">
-        <f aca="false">Portfolio!K8*MAX(0,1-ABS(Portfolio!F8-5)/MAX(2,5))</f>
-        <v>0.015106904138341</v>
-      </c>
-      <c r="E8" s="23" t="n">
-        <f aca="false">Portfolio!K8*MAX(0,1-ABS(Portfolio!F8-10)/MAX(2,10))</f>
-        <v>0.0176247214947312</v>
-      </c>
-      <c r="F8" s="23" t="n">
-        <f aca="false">Portfolio!K8*MAX(0,1-ABS(Portfolio!F8-20)/MAX(2,20))</f>
-        <v>0.00881236074736558</v>
-      </c>
-      <c r="G8" s="23" t="n">
-        <f aca="false">Portfolio!K8*MAX(0,1-ABS(Portfolio!F8-30)/MAX(2,30))</f>
-        <v>0.00587490716491039</v>
-      </c>
-      <c r="H8" s="23" t="n">
-        <f aca="false">SUM(C8:G8)</f>
-        <v>0.0474188935453481</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1" t="str">
-        <f aca="false">Portfolio!B9</f>
-        <v>HY Corporate</v>
-      </c>
-      <c r="C9" s="23" t="n">
-        <f aca="false">Portfolio!K9*MAX(0,1-ABS(Portfolio!F9-2)/MAX(2,2))</f>
-        <v>0</v>
-      </c>
-      <c r="D9" s="23" t="n">
-        <f aca="false">Portfolio!K9*MAX(0,1-ABS(Portfolio!F9-5)/MAX(2,5))</f>
-        <v>0.00982537182582354</v>
-      </c>
-      <c r="E9" s="23" t="n">
-        <f aca="false">Portfolio!K9*MAX(0,1-ABS(Portfolio!F9-10)/MAX(2,10))</f>
-        <v>0.00491268591291177</v>
-      </c>
-      <c r="F9" s="23" t="n">
-        <f aca="false">Portfolio!K9*MAX(0,1-ABS(Portfolio!F9-20)/MAX(2,20))</f>
-        <v>0.00245634295645588</v>
-      </c>
-      <c r="G9" s="23" t="n">
-        <f aca="false">Portfolio!K9*MAX(0,1-ABS(Portfolio!F9-30)/MAX(2,30))</f>
-        <v>0.00163756197097059</v>
-      </c>
-      <c r="H9" s="23" t="n">
-        <f aca="false">SUM(C9:G9)</f>
-        <v>0.0188319626661618</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="str">
-        <f aca="false">Portfolio!B10</f>
-        <v>Municipal</v>
-      </c>
-      <c r="C10" s="23" t="n">
-        <f aca="false">Portfolio!K10*MAX(0,1-ABS(Portfolio!F10-2)/MAX(2,2))</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="23" t="n">
-        <f aca="false">Portfolio!K10*MAX(0,1-ABS(Portfolio!F10-5)/MAX(2,5))</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="23" t="n">
-        <f aca="false">Portfolio!K10*MAX(0,1-ABS(Portfolio!F10-10)/MAX(2,10))</f>
-        <v>0.0149602421705348</v>
-      </c>
-      <c r="F10" s="23" t="n">
-        <f aca="false">Portfolio!K10*MAX(0,1-ABS(Portfolio!F10-20)/MAX(2,20))</f>
-        <v>0.0112201816279011</v>
-      </c>
-      <c r="G10" s="23" t="n">
-        <f aca="false">Portfolio!K10*MAX(0,1-ABS(Portfolio!F10-30)/MAX(2,30))</f>
-        <v>0.00748012108526741</v>
-      </c>
-      <c r="H10" s="23" t="n">
-        <f aca="false">SUM(C10:G10)</f>
-        <v>0.0336605448837034</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="C12" s="28" t="n">
-        <f aca="false">SUM(C5:C10)</f>
-        <v>0.00568009464399378</v>
-      </c>
-      <c r="D12" s="28" t="n">
-        <f aca="false">SUM(D5:D10)</f>
-        <v>0.0450023471594298</v>
-      </c>
-      <c r="E12" s="28" t="n">
-        <f aca="false">SUM(E5:E10)</f>
-        <v>0.0861827545304956</v>
-      </c>
-      <c r="F12" s="28" t="n">
-        <f aca="false">SUM(F5:F10)</f>
-        <v>0.0468314378078815</v>
-      </c>
-      <c r="G12" s="28" t="n">
-        <f aca="false">SUM(G5:G10)</f>
-        <v>0.0312209585385877</v>
-      </c>
-      <c r="H12" s="28" t="n">
-        <f aca="false">SUM(H5:H10)</f>
-        <v>0.214917592680388</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:H2"/>
-  </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="B2:G12"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="18"/>
-  </cols>
-  <sheetData>
-    <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="str">
-        <f aca="false">Portfolio!B5</f>
-        <v>2Y Treasury</v>
-      </c>
-      <c r="C5" s="23" t="n">
-        <f aca="false">Portfolio!C5*Portfolio!D5</f>
-        <v>1.35</v>
-      </c>
-      <c r="D5" s="23" t="n">
-        <f aca="false">Portfolio!C5*Assumptions!E13</f>
-        <v>1.8</v>
-      </c>
-      <c r="E5" s="14" t="n">
-        <f aca="false">MAX(0,Portfolio!E5-0.002)</f>
-        <v>0.042</v>
-      </c>
-      <c r="F5" s="23" t="n">
-        <f aca="false">Portfolio!C5*Portfolio!I5*(Portfolio!E5-E5)</f>
-        <v>0.113601892879876</v>
-      </c>
-      <c r="G5" s="23" t="n">
-        <f aca="false">C5-D5+F5</f>
-        <v>-0.336398107120124</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="str">
-        <f aca="false">Portfolio!B6</f>
-        <v>5Y Treasury</v>
-      </c>
-      <c r="C6" s="23" t="n">
-        <f aca="false">Portfolio!C6*Portfolio!D6</f>
-        <v>1.72</v>
-      </c>
-      <c r="D6" s="23" t="n">
-        <f aca="false">Portfolio!C6*Assumptions!E13</f>
-        <v>2.4</v>
-      </c>
-      <c r="E6" s="14" t="n">
-        <f aca="false">MAX(0,Portfolio!E6-0.002)</f>
-        <v>0.043</v>
-      </c>
-      <c r="F6" s="23" t="n">
-        <f aca="false">Portfolio!C6*Portfolio!I6*(Portfolio!E6-E6)</f>
-        <v>0.355960666753355</v>
-      </c>
-      <c r="G6" s="23" t="n">
-        <f aca="false">C6-D6+F6</f>
-        <v>-0.324039333246645</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="str">
-        <f aca="false">Portfolio!B7</f>
-        <v>10Y Treasury</v>
-      </c>
-      <c r="C7" s="23" t="n">
-        <f aca="false">Portfolio!C7*Portfolio!D7</f>
-        <v>2.5</v>
-      </c>
-      <c r="D7" s="23" t="n">
-        <f aca="false">Portfolio!C7*Assumptions!E13</f>
-        <v>3</v>
-      </c>
-      <c r="E7" s="14" t="n">
-        <f aca="false">MAX(0,Portfolio!E7-0.002)</f>
-        <v>0.053</v>
-      </c>
-      <c r="F7" s="23" t="n">
-        <f aca="false">Portfolio!C7*Portfolio!I7*(Portfolio!E7-E7)</f>
-        <v>0.773001387093704</v>
-      </c>
-      <c r="G7" s="23" t="n">
-        <f aca="false">C7-D7+F7</f>
-        <v>0.273001387093704</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="str">
-        <f aca="false">Portfolio!B8</f>
-        <v>IG Corporate</v>
-      </c>
-      <c r="C8" s="23" t="n">
-        <f aca="false">Portfolio!C8*Portfolio!D8</f>
-        <v>2.7</v>
-      </c>
-      <c r="D8" s="23" t="n">
-        <f aca="false">Portfolio!C8*Assumptions!E13</f>
-        <v>2.7</v>
-      </c>
-      <c r="E8" s="14" t="n">
-        <f aca="false">MAX(0,Portfolio!E8-0.002)</f>
-        <v>0.066</v>
-      </c>
-      <c r="F8" s="23" t="n">
-        <f aca="false">Portfolio!C8*Portfolio!I8*(Portfolio!E8-E8)</f>
-        <v>0.503563471278034</v>
-      </c>
-      <c r="G8" s="23" t="n">
-        <f aca="false">C8-D8+F8</f>
-        <v>0.503563471278034</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1" t="str">
-        <f aca="false">Portfolio!B9</f>
-        <v>HY Corporate</v>
-      </c>
-      <c r="C9" s="23" t="n">
-        <f aca="false">Portfolio!C9*Portfolio!D9</f>
-        <v>2.125</v>
-      </c>
-      <c r="D9" s="23" t="n">
-        <f aca="false">Portfolio!C9*Assumptions!E13</f>
-        <v>1.5</v>
-      </c>
-      <c r="E9" s="14" t="n">
-        <f aca="false">MAX(0,Portfolio!E9-0.002)</f>
-        <v>0.103</v>
-      </c>
-      <c r="F9" s="23" t="n">
-        <f aca="false">Portfolio!C9*Portfolio!I9*(Portfolio!E9-E9)</f>
-        <v>0.196507436516471</v>
-      </c>
-      <c r="G9" s="23" t="n">
-        <f aca="false">C9-D9+F9</f>
-        <v>0.821507436516471</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="str">
-        <f aca="false">Portfolio!B10</f>
-        <v>Municipal</v>
-      </c>
-      <c r="C10" s="23" t="n">
-        <f aca="false">Portfolio!C10*Portfolio!D10</f>
-        <v>0.8</v>
-      </c>
-      <c r="D10" s="23" t="n">
-        <f aca="false">Portfolio!C10*Assumptions!E13</f>
-        <v>1.2</v>
-      </c>
-      <c r="E10" s="14" t="n">
-        <f aca="false">MAX(0,Portfolio!E10-0.002)</f>
-        <v>0.044</v>
-      </c>
-      <c r="F10" s="23" t="n">
-        <f aca="false">Portfolio!C10*Portfolio!I10*(Portfolio!E10-E10)</f>
-        <v>0.374006054263371</v>
-      </c>
-      <c r="G10" s="23" t="n">
-        <f aca="false">C10-D10+F10</f>
-        <v>-0.0259939457366291</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="27" t="s">
-        <v>105</v>
-      </c>
-      <c r="C12" s="28" t="n">
-        <f aca="false">SUM(C5:C10)</f>
-        <v>11.195</v>
-      </c>
-      <c r="D12" s="28" t="n">
-        <f aca="false">SUM(D5:D10)</f>
-        <v>12.6</v>
-      </c>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28" t="n">
-        <f aca="false">SUM(F5:F10)</f>
-        <v>2.31664090878481</v>
-      </c>
-      <c r="G12" s="28" t="n">
-        <f aca="false">SUM(G5:G10)</f>
-        <v>0.911640908784811</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:G2"/>
-  </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="B2:I10"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="18"/>
-  </cols>
-  <sheetData>
-    <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C5" s="13" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D5" s="13" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E5" s="13" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F5" s="13" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G5" s="13" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="H5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="23" t="n">
-        <f aca="false">-SUMPRODUCT('Key Rate Risk'!C12:G12,C5:G5)/0.0001-SUMPRODUCT(Portfolio!C5:C10,Portfolio!G5:G10)*H5</f>
-        <v>-21.4917592680388</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C6" s="13" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="D6" s="13" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="E6" s="13" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="F6" s="13" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="G6" s="13" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="H6" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="23" t="n">
-        <f aca="false">-SUMPRODUCT('Key Rate Risk'!C12:G12,C6:G6)/0.0001-SUMPRODUCT(Portfolio!C5:C10,Portfolio!G5:G10)*H6</f>
-        <v>21.4917592680388</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C7" s="13" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="D7" s="13" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="E7" s="13" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="F7" s="13" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G7" s="13" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="H7" s="13" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="I7" s="23" t="n">
-        <f aca="false">-SUMPRODUCT('Key Rate Risk'!C12:G12,C7:G7)/0.0001-SUMPRODUCT(Portfolio!C5:C10,Portfolio!G5:G10)*H7</f>
-        <v>-27.8556112567415</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C8" s="13" t="n">
-        <v>-0.012</v>
-      </c>
-      <c r="D8" s="13" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="E8" s="13" t="n">
-        <v>-0.008</v>
-      </c>
-      <c r="F8" s="13" t="n">
-        <v>-0.006</v>
-      </c>
-      <c r="G8" s="13" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="H8" s="13" t="n">
-        <v>-0.001</v>
-      </c>
-      <c r="I8" s="23" t="n">
-        <f aca="false">-SUMPRODUCT('Key Rate Risk'!C12:G12,C8:G8)/0.0001-SUMPRODUCT(Portfolio!C5:C10,Portfolio!G5:G10)*H8</f>
-        <v>16.9399006310642</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C9" s="13" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="D9" s="13" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="E9" s="13" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="F9" s="13" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="H9" s="13" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="I9" s="23" t="n">
-        <f aca="false">-SUMPRODUCT('Key Rate Risk'!C12:G12,C9:G9)/0.0001-SUMPRODUCT(Portfolio!C5:C10,Portfolio!G5:G10)*H9</f>
-        <v>-16.2011023062061</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C10" s="13" t="n">
-        <v>-0.008</v>
-      </c>
-      <c r="D10" s="13" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="E10" s="13" t="n">
-        <v>-0.012</v>
-      </c>
-      <c r="F10" s="13" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="G10" s="13" t="n">
-        <v>-0.008</v>
-      </c>
-      <c r="H10" s="13" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I10" s="23" t="n">
-        <f aca="false">-SUMPRODUCT('Key Rate Risk'!C12:G12,C10:G10)/0.0001-SUMPRODUCT(Portfolio!C5:C10,Portfolio!G5:G10)*H10</f>
-        <v>12.6273932949971</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:H2"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3623,186 +4997,261 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:F15"/>
+  <dimension ref="B2:H12"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="16"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>116</v>
+        <v>192</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>121</v>
+      <c r="B4" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C5" s="23" t="n">
-        <f aca="false">'Carry &amp; Roll'!C12-'Carry &amp; Roll'!D12</f>
-        <v>-1.405</v>
-      </c>
-      <c r="D5" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="23" t="n">
-        <f aca="false">C5*D5</f>
-        <v>-1.405</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>123</v>
+      <c r="B5" s="1" t="str">
+        <f aca="false">Portfolio!B5</f>
+        <v>2Y Treasury</v>
+      </c>
+      <c r="C5" s="29" t="n">
+        <f aca="false">Portfolio!K5*MAX(0,1-ABS(Portfolio!F5-2)/MAX(2,2))</f>
+        <v>0.00568009464399378</v>
+      </c>
+      <c r="D5" s="29" t="n">
+        <f aca="false">Portfolio!K5*MAX(0,1-ABS(Portfolio!F5-5)/MAX(2,5))</f>
+        <v>0.00227203785759751</v>
+      </c>
+      <c r="E5" s="29" t="n">
+        <f aca="false">Portfolio!K5*MAX(0,1-ABS(Portfolio!F5-10)/MAX(2,10))</f>
+        <v>0.00113601892879876</v>
+      </c>
+      <c r="F5" s="29" t="n">
+        <f aca="false">Portfolio!K5*MAX(0,1-ABS(Portfolio!F5-20)/MAX(2,20))</f>
+        <v>0.000568009464399378</v>
+      </c>
+      <c r="G5" s="29" t="n">
+        <f aca="false">Portfolio!K5*MAX(0,1-ABS(Portfolio!F5-30)/MAX(2,30))</f>
+        <v>0.000378672976266252</v>
+      </c>
+      <c r="H5" s="29" t="n">
+        <f aca="false">SUM(C5:G5)</f>
+        <v>0.0100348338710557</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C6" s="23" t="n">
-        <f aca="false">'Carry &amp; Roll'!F12</f>
-        <v>2.31664090878481</v>
-      </c>
-      <c r="D6" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="23" t="n">
-        <f aca="false">C6*D6</f>
-        <v>2.31664090878481</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>125</v>
+      <c r="B6" s="1" t="str">
+        <f aca="false">Portfolio!B6</f>
+        <v>5Y Treasury</v>
+      </c>
+      <c r="C6" s="29" t="n">
+        <f aca="false">Portfolio!K6*MAX(0,1-ABS(Portfolio!F6-2)/MAX(2,2))</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="29" t="n">
+        <f aca="false">Portfolio!K6*MAX(0,1-ABS(Portfolio!F6-5)/MAX(2,5))</f>
+        <v>0.0177980333376678</v>
+      </c>
+      <c r="E6" s="29" t="n">
+        <f aca="false">Portfolio!K6*MAX(0,1-ABS(Portfolio!F6-10)/MAX(2,10))</f>
+        <v>0.00889901666883388</v>
+      </c>
+      <c r="F6" s="29" t="n">
+        <f aca="false">Portfolio!K6*MAX(0,1-ABS(Portfolio!F6-20)/MAX(2,20))</f>
+        <v>0.00444950833441694</v>
+      </c>
+      <c r="G6" s="29" t="n">
+        <f aca="false">Portfolio!K6*MAX(0,1-ABS(Portfolio!F6-30)/MAX(2,30))</f>
+        <v>0.00296633888961129</v>
+      </c>
+      <c r="H6" s="29" t="n">
+        <f aca="false">SUM(C6:G6)</f>
+        <v>0.0341128972305299</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C7" s="23" t="n">
-        <f aca="false">-Portfolio!K12/0.0001</f>
-        <v>-1158.3204543924</v>
-      </c>
-      <c r="D7" s="13" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="E7" s="23" t="n">
-        <f aca="false">C7*D7</f>
-        <v>-0.579160227196202</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>127</v>
+      <c r="B7" s="1" t="str">
+        <f aca="false">Portfolio!B7</f>
+        <v>10Y Treasury</v>
+      </c>
+      <c r="C7" s="29" t="n">
+        <f aca="false">Portfolio!K7*MAX(0,1-ABS(Portfolio!F7-2)/MAX(2,2))</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="29" t="n">
+        <f aca="false">Portfolio!K7*MAX(0,1-ABS(Portfolio!F7-5)/MAX(2,5))</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="29" t="n">
+        <f aca="false">Portfolio!K7*MAX(0,1-ABS(Portfolio!F7-10)/MAX(2,10))</f>
+        <v>0.0386500693546852</v>
+      </c>
+      <c r="F7" s="29" t="n">
+        <f aca="false">Portfolio!K7*MAX(0,1-ABS(Portfolio!F7-20)/MAX(2,20))</f>
+        <v>0.0193250346773426</v>
+      </c>
+      <c r="G7" s="29" t="n">
+        <f aca="false">Portfolio!K7*MAX(0,1-ABS(Portfolio!F7-30)/MAX(2,30))</f>
+        <v>0.0128833564515617</v>
+      </c>
+      <c r="H7" s="29" t="n">
+        <f aca="false">SUM(C7:G7)</f>
+        <v>0.0708584604835895</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C8" s="23" t="n">
-        <f aca="false">-('Key Rate Risk'!C12*0.0002+'Key Rate Risk'!D12*0.0001-'Key Rate Risk'!F12*0.0001)/0.0001</f>
-        <v>-0.00953109863953586</v>
-      </c>
-      <c r="D8" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="23" t="n">
-        <f aca="false">C8*D8</f>
-        <v>-0.00953109863953586</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>129</v>
+      <c r="B8" s="1" t="str">
+        <f aca="false">Portfolio!B8</f>
+        <v>IG Corporate</v>
+      </c>
+      <c r="C8" s="29" t="n">
+        <f aca="false">Portfolio!K8*MAX(0,1-ABS(Portfolio!F8-2)/MAX(2,2))</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="29" t="n">
+        <f aca="false">Portfolio!K8*MAX(0,1-ABS(Portfolio!F8-5)/MAX(2,5))</f>
+        <v>0.015106904138341</v>
+      </c>
+      <c r="E8" s="29" t="n">
+        <f aca="false">Portfolio!K8*MAX(0,1-ABS(Portfolio!F8-10)/MAX(2,10))</f>
+        <v>0.0176247214947312</v>
+      </c>
+      <c r="F8" s="29" t="n">
+        <f aca="false">Portfolio!K8*MAX(0,1-ABS(Portfolio!F8-20)/MAX(2,20))</f>
+        <v>0.00881236074736558</v>
+      </c>
+      <c r="G8" s="29" t="n">
+        <f aca="false">Portfolio!K8*MAX(0,1-ABS(Portfolio!F8-30)/MAX(2,30))</f>
+        <v>0.00587490716491039</v>
+      </c>
+      <c r="H8" s="29" t="n">
+        <f aca="false">SUM(C8:G8)</f>
+        <v>0.0474188935453481</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C9" s="23" t="n">
-        <f aca="false">-SUMPRODUCT(Portfolio!C5:C10,Portfolio!G5:G10)</f>
-        <v>-492.5</v>
-      </c>
-      <c r="D9" s="13" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="E9" s="23" t="n">
-        <f aca="false">C9*D9</f>
-        <v>-0.73875</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>130</v>
+      <c r="B9" s="1" t="str">
+        <f aca="false">Portfolio!B9</f>
+        <v>HY Corporate</v>
+      </c>
+      <c r="C9" s="29" t="n">
+        <f aca="false">Portfolio!K9*MAX(0,1-ABS(Portfolio!F9-2)/MAX(2,2))</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="29" t="n">
+        <f aca="false">Portfolio!K9*MAX(0,1-ABS(Portfolio!F9-5)/MAX(2,5))</f>
+        <v>0.00982537182582354</v>
+      </c>
+      <c r="E9" s="29" t="n">
+        <f aca="false">Portfolio!K9*MAX(0,1-ABS(Portfolio!F9-10)/MAX(2,10))</f>
+        <v>0.00491268591291177</v>
+      </c>
+      <c r="F9" s="29" t="n">
+        <f aca="false">Portfolio!K9*MAX(0,1-ABS(Portfolio!F9-20)/MAX(2,20))</f>
+        <v>0.00245634295645588</v>
+      </c>
+      <c r="G9" s="29" t="n">
+        <f aca="false">Portfolio!K9*MAX(0,1-ABS(Portfolio!F9-30)/MAX(2,30))</f>
+        <v>0.00163756197097059</v>
+      </c>
+      <c r="H9" s="29" t="n">
+        <f aca="false">SUM(C9:G9)</f>
+        <v>0.0188319626661618</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C10" s="23" t="n">
-        <f aca="false">0.5*SUMPRODUCT(Portfolio!C5:C10,Portfolio!J5:J10)</f>
-        <v>4496.45840799893</v>
-      </c>
-      <c r="D10" s="13" t="n">
-        <v>2.5E-007</v>
-      </c>
-      <c r="E10" s="23" t="n">
-        <f aca="false">C10*D10</f>
-        <v>0.00112411460199973</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E13" s="23" t="n">
+      <c r="B10" s="1" t="str">
+        <f aca="false">Portfolio!B10</f>
+        <v>Municipal</v>
+      </c>
+      <c r="C10" s="29" t="n">
+        <f aca="false">Portfolio!K10*MAX(0,1-ABS(Portfolio!F10-2)/MAX(2,2))</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="29" t="n">
+        <f aca="false">Portfolio!K10*MAX(0,1-ABS(Portfolio!F10-5)/MAX(2,5))</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="29" t="n">
+        <f aca="false">Portfolio!K10*MAX(0,1-ABS(Portfolio!F10-10)/MAX(2,10))</f>
+        <v>0.0149602421705348</v>
+      </c>
+      <c r="F10" s="29" t="n">
+        <f aca="false">Portfolio!K10*MAX(0,1-ABS(Portfolio!F10-20)/MAX(2,20))</f>
+        <v>0.0112201816279011</v>
+      </c>
+      <c r="G10" s="29" t="n">
+        <f aca="false">Portfolio!K10*MAX(0,1-ABS(Portfolio!F10-30)/MAX(2,30))</f>
+        <v>0.00748012108526741</v>
+      </c>
+      <c r="H10" s="29" t="n">
+        <f aca="false">SUM(C10:G10)</f>
+        <v>0.0336605448837034</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="33" t="s">
+        <v>199</v>
+      </c>
+      <c r="C12" s="34" t="n">
+        <f aca="false">SUM(C5:C10)</f>
+        <v>0.00568009464399378</v>
+      </c>
+      <c r="D12" s="34" t="n">
+        <f aca="false">SUM(D5:D10)</f>
+        <v>0.0450023471594298</v>
+      </c>
+      <c r="E12" s="34" t="n">
         <f aca="false">SUM(E5:E10)</f>
-        <v>-0.414676302448925</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E14" s="22" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E15" s="23" t="n">
-        <f aca="false">E14-E13</f>
-        <v>1.61467630244892</v>
+        <v>0.0861827545304956</v>
+      </c>
+      <c r="F12" s="34" t="n">
+        <f aca="false">SUM(F5:F10)</f>
+        <v>0.0468314378078815</v>
+      </c>
+      <c r="G12" s="34" t="n">
+        <f aca="false">SUM(G5:G10)</f>
+        <v>0.0312209585385877</v>
+      </c>
+      <c r="H12" s="34" t="n">
+        <f aca="false">SUM(H5:H10)</f>
+        <v>0.214917592680388</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B2:H2"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
